--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91907</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75109</v>
+        <v>75113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,42 +988,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128635712</v>
+        <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>98572</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581281</v>
+        <v>581301</v>
       </c>
       <c r="R5" t="n">
-        <v>6846302</v>
+        <v>6846334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,37 +1089,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128635763</v>
+        <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>92779</v>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1137,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581301</v>
+        <v>581281</v>
       </c>
       <c r="R6" t="n">
-        <v>6846334</v>
+        <v>6846302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,6 +1168,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75113</v>
+        <v>75115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>91975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75150</v>
+        <v>75155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91975</v>
+        <v>91981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128635624</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128635763</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40120-2025 artfynd.xlsx
+++ b/artfynd/A 40120-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>128635457</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -695,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -776,42 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128635624</v>
+        <v>128635763</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581239</v>
+        <v>581301</v>
       </c>
       <c r="R3" t="n">
-        <v>6846129</v>
+        <v>6846334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +850,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 70 plantor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,11 +880,11 @@
         <v>128635516</v>
       </c>
       <c r="B4" t="n">
-        <v>75157</v>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -988,37 +978,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128635763</v>
+        <v>128635624</v>
       </c>
       <c r="B5" t="n">
-        <v>92864</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581301</v>
+        <v>581239</v>
       </c>
       <c r="R5" t="n">
-        <v>6846334</v>
+        <v>6846129</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 70 plantor.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,7 +1092,7 @@
         <v>128635712</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
